--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Image/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Image/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7e5722d4e54f446d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R12472d81ced849a7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -64,7 +64,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R70f4916b817b4b00"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R81cfe3f6940e4832"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -93,6 +93,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44cfe08b57f0461c"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re58e6f47013b40f7"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Image/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Image/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R12472d81ced849a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rec6a0919c59c42a0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -64,7 +64,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R81cfe3f6940e4832"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R8df36fede4264935"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -93,6 +93,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re58e6f47013b40f7"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8da72aef903b4a3a"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Image/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Image/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rec6a0919c59c42a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R733b2ebd4f6d4df1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -64,7 +64,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R8df36fede4264935"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R0e831a91cdf14cf1"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -93,6 +93,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8da72aef903b4a3a"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c290286d46c459b"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Image/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Image/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R733b2ebd4f6d4df1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9688c5d80cfe4c10"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -64,7 +64,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R0e831a91cdf14cf1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R017538c1b64d4357"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -93,6 +93,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c290286d46c459b"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47d9dd99c83c45ca"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Image/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Image/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9688c5d80cfe4c10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5275ff68e81746a4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -64,7 +64,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R017538c1b64d4357"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R5e871be815094fe8"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -93,6 +93,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47d9dd99c83c45ca"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R50908765045b412a"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Image/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Image/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5275ff68e81746a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd6ec7f9ee36442f4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -64,7 +64,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R5e871be815094fe8"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R8f15bd1e08ef40f6"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -93,6 +93,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R50908765045b412a"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95aef17ae155491e"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Image/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Image/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd6ec7f9ee36442f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9a5d085dc8e745f9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -64,7 +64,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R8f15bd1e08ef40f6"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R4b23a97b4afe4c2c"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -93,6 +93,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95aef17ae155491e"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R66ab26e678254a4a"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Image/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Image/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9a5d085dc8e745f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra5deb46a73f04eac"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -64,7 +64,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R4b23a97b4afe4c2c"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Re52bb1e7a602425b"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -93,6 +93,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R66ab26e678254a4a"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R107e6d992f3f4af5"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Image/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Image/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra5deb46a73f04eac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R81a475ad0ef64c9b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -64,7 +64,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Re52bb1e7a602425b"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rfadfb5e356fa4a66"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -93,6 +93,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R107e6d992f3f4af5"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61d0f3824b374844"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Image/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Image/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R81a475ad0ef64c9b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R42d39945f60e416c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -64,7 +64,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rfadfb5e356fa4a66"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R3a8245e5b5d14212"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -93,6 +93,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61d0f3824b374844"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R172f6d8c4fe344ee"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Image/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Image/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R42d39945f60e416c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5d12975a595e40cc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -64,7 +64,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R3a8245e5b5d14212"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rcd1983333f794ad7"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -93,6 +93,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R172f6d8c4fe344ee"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73341ab438dc484d"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Image/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Image/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5d12975a595e40cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdd39a9b557fb40e7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -64,7 +64,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rcd1983333f794ad7"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R825e903c33fa4436"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -93,6 +93,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73341ab438dc484d"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a1fb7d082c04795"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Image/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Image/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdd39a9b557fb40e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4c1d933889cc4c85"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -64,7 +64,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R825e903c33fa4436"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R9fd0c0d0b2714ab1"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -93,6 +93,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a1fb7d082c04795"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44bf6323a32b401d"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Image/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Image/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4c1d933889cc4c85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb3ae4a8932834f75"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -64,7 +64,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R9fd0c0d0b2714ab1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rdc37b9bb4873465e"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -93,6 +93,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44bf6323a32b401d"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc74975b119474eb0"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Image/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Image/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb3ae4a8932834f75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8cd54117ed7f4680"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -64,7 +64,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rdc37b9bb4873465e"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R9f24d670b49f4ed1"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -93,6 +93,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc74975b119474eb0"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1522634c21b74430"/>
 </x:worksheet>
 </file>